--- a/EXCEL/Data/løn_data/løn_stilling.xlsx
+++ b/EXCEL/Data/løn_data/løn_stilling.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="93">
   <si>
     <t xml:space="preserve">Lønniveau - feb 2025 </t>
   </si>
@@ -28,6 +28,18 @@
     <t>Fuldtid</t>
   </si>
   <si>
+    <t>Lokale tillæg</t>
+  </si>
+  <si>
+    <t>Særydelser</t>
+  </si>
+  <si>
+    <t>Overarbejde</t>
+  </si>
+  <si>
+    <t>Nettoløn</t>
+  </si>
+  <si>
     <t>Bruttoløn</t>
   </si>
   <si>
@@ -166,7 +178,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 14.26.07</t>
+    <t>Kørsel 10.4.2026 10.34.28</t>
   </si>
   <si>
     <t/>
@@ -269,9 +281,6 @@
   </si>
   <si>
     <t>Lokalt aftalte tillæg</t>
-  </si>
-  <si>
-    <t>Særydelser</t>
   </si>
   <si>
     <t>Feriegodtgørelse</t>
@@ -729,16 +738,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="4" max="9" width="18" customWidth="1"/>
+    <col min="10" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,8 +755,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -763,2881 +776,4717 @@
       <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5">
-        <v>81010.25769676926</v>
+        <v>81010.25769676956</v>
       </c>
       <c r="E3" s="6">
-        <v>53754.26860401571</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3567.0690457168084</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3432.929956335347</v>
+      </c>
+      <c r="G3" s="6">
+        <v>606.6435097852317</v>
+      </c>
+      <c r="H3" s="6">
+        <v>42196.58992893077</v>
+      </c>
+      <c r="I3" s="6">
+        <v>53770.56370637268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" s="8">
-        <v>4830.921400403814</v>
+        <v>4830.921400403811</v>
       </c>
       <c r="E4" s="9">
-        <v>44028.82142087667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3152.348879540617</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1390.3566638220484</v>
+      </c>
+      <c r="G4" s="9">
+        <v>340.68899276176535</v>
+      </c>
+      <c r="H4" s="9">
+        <v>35662.60345179296</v>
+      </c>
+      <c r="I4" s="9">
+        <v>44038.66560004599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>1225.9471332894805</v>
+        <v>1225.9471332894807</v>
       </c>
       <c r="E5" s="6">
-        <v>42322.344616865026</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2622.9594582955997</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1012.7554508947708</v>
+      </c>
+      <c r="G5" s="6">
+        <v>275.07238826790694</v>
+      </c>
+      <c r="H5" s="6">
+        <v>34282.587151734435</v>
+      </c>
+      <c r="I5" s="6">
+        <v>42330.530333749586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="8">
-        <v>144.84027958944736</v>
+        <v>144.84027958944742</v>
       </c>
       <c r="E6" s="9">
-        <v>41655.042137323435</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1649.7556030210073</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1428.9121011934496</v>
+      </c>
+      <c r="G6" s="9">
+        <v>91.06065465320309</v>
+      </c>
+      <c r="H6" s="9">
+        <v>33382.917352421595</v>
+      </c>
+      <c r="I6" s="9">
+        <v>41657.57433651713</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5">
-        <v>378.82062942865804</v>
+        <v>378.8206294286582</v>
       </c>
       <c r="E7" s="6">
-        <v>42041.906144421904</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2258.7800125835147</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1420.0276344584072</v>
+      </c>
+      <c r="G7" s="6">
+        <v>425.2753093440016</v>
+      </c>
+      <c r="H7" s="6">
+        <v>33666.73684179872</v>
+      </c>
+      <c r="I7" s="6">
+        <v>42054.1834113657</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="8">
+        <v>234.40570624683593</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2778.062013229002</v>
+      </c>
+      <c r="F8" s="9">
+        <v>992.8136998989428</v>
+      </c>
+      <c r="G8" s="9">
+        <v>218.05206612122933</v>
+      </c>
+      <c r="H8" s="9">
+        <v>34282.394409017645</v>
+      </c>
+      <c r="I8" s="9">
+        <v>42307.54570994345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8">
-        <v>234.40570624683585</v>
-      </c>
-      <c r="E8" s="9">
-        <v>42301.24769231248</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5">
+        <v>318.6540207655224</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3199.2213990618097</v>
+      </c>
+      <c r="F9" s="6">
+        <v>547.2496116105965</v>
+      </c>
+      <c r="G9" s="6">
+        <v>270.13521142117827</v>
+      </c>
+      <c r="H9" s="6">
+        <v>35170.95203912017</v>
+      </c>
+      <c r="I9" s="6">
+        <v>42897.47275600873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="5">
-        <v>318.65402076552226</v>
-      </c>
-      <c r="E9" s="6">
-        <v>42888.70166094169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="C10" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D10" s="8">
         <v>116.96166791999205</v>
       </c>
       <c r="E10" s="9">
-        <v>42879.14486469255</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3250.7005871582933</v>
+      </c>
+      <c r="F10" s="9">
+        <v>729.7898390113446</v>
+      </c>
+      <c r="G10" s="9">
+        <v>220.06846712016267</v>
+      </c>
+      <c r="H10" s="9">
+        <v>35014.19231113873</v>
+      </c>
+      <c r="I10" s="9">
+        <v>42885.52621809585</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
         <v>32.2648293390232</v>
       </c>
       <c r="E11" s="6">
-        <v>41151.94204887437</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2173.8961043405393</v>
+      </c>
+      <c r="F11" s="6">
+        <v>130.88334563552988</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>34127.60738675258</v>
+      </c>
+      <c r="I11" s="6">
+        <v>41151.94204887438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="8">
         <v>1797.594087690101</v>
       </c>
       <c r="E12" s="9">
-        <v>42497.98502177882</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2791.359847308892</v>
+      </c>
+      <c r="F12" s="9">
+        <v>496.09411795688584</v>
+      </c>
+      <c r="G12" s="9">
+        <v>109.47446398793551</v>
+      </c>
+      <c r="H12" s="9">
+        <v>34907.468690117785</v>
+      </c>
+      <c r="I12" s="9">
+        <v>42501.40224197101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5">
         <v>180.94300037631803</v>
       </c>
       <c r="E13" s="6">
-        <v>41917.07304508802</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1993.3866428156293</v>
+      </c>
+      <c r="F13" s="6">
+        <v>976.8947716047815</v>
+      </c>
+      <c r="G13" s="6">
+        <v>73.41435994050258</v>
+      </c>
+      <c r="H13" s="6">
+        <v>34044.0343552628</v>
+      </c>
+      <c r="I13" s="6">
+        <v>41919.230241088284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8">
+        <v>463.95402098377286</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2582.0114304325366</v>
+      </c>
+      <c r="F14" s="9">
+        <v>701.547709527675</v>
+      </c>
+      <c r="G14" s="9">
+        <v>141.0089567844889</v>
+      </c>
+      <c r="H14" s="9">
+        <v>34394.286914814555</v>
+      </c>
+      <c r="I14" s="9">
+        <v>42114.01240189501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D15" s="5">
+        <v>369.9433575182688</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2946.5074979208957</v>
+      </c>
+      <c r="F15" s="6">
+        <v>293.1473723399539</v>
+      </c>
+      <c r="G15" s="6">
+        <v>84.6793632730865</v>
+      </c>
+      <c r="H15" s="6">
+        <v>34982.99747634204</v>
+      </c>
+      <c r="I15" s="6">
+        <v>42372.75082270347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8">
+        <v>506.7503489044608</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3079.598040238618</v>
+      </c>
+      <c r="F16" s="9">
+        <v>374.30252115726336</v>
+      </c>
+      <c r="G16" s="9">
+        <v>122.58575847671678</v>
+      </c>
+      <c r="H16" s="9">
+        <v>35605.08726725031</v>
+      </c>
+      <c r="I16" s="9">
+        <v>43231.976669941396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>226.83061943494113</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2812.9098136459693</v>
+      </c>
+      <c r="F17" s="6">
+        <v>369.9166324895731</v>
+      </c>
+      <c r="G17" s="6">
+        <v>108.61945528055689</v>
+      </c>
+      <c r="H17" s="6">
+        <v>34787.42406036046</v>
+      </c>
+      <c r="I17" s="6">
+        <v>42216.74978248182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8">
+        <v>49.17274047234177</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3465.8568448819315</v>
+      </c>
+      <c r="F18" s="9">
+        <v>152.38984611120216</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>35722.86182333281</v>
+      </c>
+      <c r="I18" s="9">
+        <v>43050.767759023365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="8">
-        <v>463.9540209837727</v>
-      </c>
-      <c r="E14" s="9">
-        <v>42109.49838555551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="D19" s="5">
+        <v>1807.3801794241847</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3870.468513807921</v>
+      </c>
+      <c r="F19" s="6">
+        <v>2535.90435399558</v>
+      </c>
+      <c r="G19" s="6">
+        <v>615.1593912616431</v>
+      </c>
+      <c r="H19" s="6">
+        <v>37349.71546323525</v>
+      </c>
+      <c r="I19" s="6">
+        <v>46726.234663813855</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="8">
+        <v>165.1782941154424</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2407.2552002956672</v>
+      </c>
+      <c r="F20" s="9">
+        <v>3027.498837308272</v>
+      </c>
+      <c r="G20" s="9">
+        <v>89.93056980726287</v>
+      </c>
+      <c r="H20" s="9">
+        <v>35735.92437451158</v>
+      </c>
+      <c r="I20" s="9">
+        <v>45462.54236022988</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="5">
+        <v>431.2120651798456</v>
+      </c>
+      <c r="E21" s="6">
+        <v>3099.722929540087</v>
+      </c>
+      <c r="F21" s="6">
+        <v>2186.8624034682202</v>
+      </c>
+      <c r="G21" s="6">
+        <v>102.73198590143556</v>
+      </c>
+      <c r="H21" s="6">
+        <v>36675.51122590948</v>
+      </c>
+      <c r="I21" s="6">
+        <v>45498.83833256704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D22" s="8">
+        <v>394.9195967099158</v>
+      </c>
+      <c r="E22" s="9">
+        <v>3800.792292563588</v>
+      </c>
+      <c r="F22" s="9">
+        <v>2182.706430375487</v>
+      </c>
+      <c r="G22" s="9">
+        <v>406.14858616347703</v>
+      </c>
+      <c r="H22" s="9">
+        <v>37143.97387880929</v>
+      </c>
+      <c r="I22" s="9">
+        <v>46045.10455060124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="5">
-        <v>369.94335751826856</v>
-      </c>
-      <c r="E15" s="6">
-        <v>42369.9491793938</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="5">
+        <v>632.564391212121</v>
+      </c>
+      <c r="E23" s="6">
+        <v>4625.010814746279</v>
+      </c>
+      <c r="F23" s="6">
+        <v>2255.741473204108</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1150.162551500819</v>
+      </c>
+      <c r="H23" s="6">
+        <v>38296.7632879989</v>
+      </c>
+      <c r="I23" s="6">
+        <v>47608.43220773919</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="8">
+        <v>183.5058322068561</v>
+      </c>
+      <c r="E24" s="9">
+        <v>4547.64474649841</v>
+      </c>
+      <c r="F24" s="9">
+        <v>4639.468045742157</v>
+      </c>
+      <c r="G24" s="9">
+        <v>897.6561073001672</v>
+      </c>
+      <c r="H24" s="9">
+        <v>37564.80897267486</v>
+      </c>
+      <c r="I24" s="9">
+        <v>49172.73741361704</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2047.9265256567153</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1329.5056054826912</v>
+      </c>
+      <c r="F25" s="6">
+        <v>1619.3119729675568</v>
+      </c>
+      <c r="G25" s="6">
+        <v>53.34495250249488</v>
+      </c>
+      <c r="H25" s="6">
+        <v>27907.912313517798</v>
+      </c>
+      <c r="I25" s="6">
+        <v>33942.11638363369</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2047.9265256567153</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1329.5056054826912</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1619.3119729675568</v>
+      </c>
+      <c r="G26" s="9">
+        <v>53.34495250249488</v>
+      </c>
+      <c r="H26" s="9">
+        <v>27907.912313517798</v>
+      </c>
+      <c r="I26" s="9">
+        <v>33942.11638363369</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="5">
+        <v>172.47713555600967</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1355.655101056432</v>
+      </c>
+      <c r="F27" s="6">
+        <v>837.1884043138307</v>
+      </c>
+      <c r="G27" s="6">
+        <v>4.451977512736754</v>
+      </c>
+      <c r="H27" s="6">
+        <v>27171.201565222327</v>
+      </c>
+      <c r="I27" s="6">
+        <v>32229.68881495149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="8">
+        <v>104.8536844088097</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1294.1095179781714</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1174.5872903070674</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3.540096901287803</v>
+      </c>
+      <c r="H28" s="9">
+        <v>26670.502048683957</v>
+      </c>
+      <c r="I28" s="9">
+        <v>31704.677705512142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8">
-        <v>506.7503489044609</v>
-      </c>
-      <c r="E16" s="9">
-        <v>43228.281409723386</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5">
-        <v>226.83061943494116</v>
-      </c>
-      <c r="E17" s="6">
-        <v>42213.44720573876</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="8">
-        <v>49.172740472341786</v>
-      </c>
-      <c r="E18" s="9">
-        <v>43050.76775902334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="D29" s="5">
+        <v>366.14903229711484</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1709.4360290290822</v>
+      </c>
+      <c r="F29" s="6">
+        <v>1242.4553652061256</v>
+      </c>
+      <c r="G29" s="6">
+        <v>65.6290259503062</v>
+      </c>
+      <c r="H29" s="6">
+        <v>27394.074624954086</v>
+      </c>
+      <c r="I29" s="6">
+        <v>32937.005554482515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1807.380179424185</v>
-      </c>
-      <c r="E19" s="6">
-        <v>46708.873388519685</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="8">
-        <v>165.17829411544247</v>
-      </c>
-      <c r="E20" s="9">
-        <v>45460.78871408245</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="D30" s="8">
+        <v>1244.2215540423294</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1134.2367102562432</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1809.4550640111922</v>
+      </c>
+      <c r="G30" s="9">
+        <v>64.00148468231471</v>
+      </c>
+      <c r="H30" s="9">
+        <v>28263.121383276186</v>
+      </c>
+      <c r="I30" s="9">
+        <v>34624.94659984054</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5">
+        <v>146.92085936757087</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1962.755234404909</v>
+      </c>
+      <c r="F31" s="6">
+        <v>2173.4731771068255</v>
+      </c>
+      <c r="G31" s="6">
+        <v>29.281519913791076</v>
+      </c>
+      <c r="H31" s="6">
+        <v>27975.686804852376</v>
+      </c>
+      <c r="I31" s="6">
+        <v>34324.60172175654</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="8">
+        <v>13.304259984882568</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2081.9151182758915</v>
+      </c>
+      <c r="F32" s="9">
+        <v>1733.347926567417</v>
+      </c>
+      <c r="G32" s="9">
+        <v>10.777718086032705</v>
+      </c>
+      <c r="H32" s="9">
+        <v>27384.597985242646</v>
+      </c>
+      <c r="I32" s="9">
+        <v>33355.19918875896</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="5">
-        <v>431.2120651798458</v>
-      </c>
-      <c r="E21" s="6">
-        <v>45496.20744675301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="8">
-        <v>394.9195967099155</v>
-      </c>
-      <c r="E22" s="9">
-        <v>46033.761364669226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="5">
-        <v>632.5643912121205</v>
-      </c>
-      <c r="E23" s="6">
-        <v>47575.24851793246</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="8">
-        <v>183.50583220685604</v>
-      </c>
-      <c r="E24" s="9">
-        <v>49148.303182488984</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2047.9265256567169</v>
-      </c>
-      <c r="E25" s="6">
-        <v>33940.550049815676</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8">
-        <v>2047.9265256567169</v>
-      </c>
-      <c r="E26" s="9">
-        <v>33940.550049815676</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="5">
-        <v>172.47713555600964</v>
-      </c>
-      <c r="E27" s="6">
-        <v>32229.557926811074</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="C33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="8">
-        <v>104.85368440880967</v>
-      </c>
-      <c r="E28" s="9">
-        <v>31704.5864799913</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="5">
-        <v>366.149032297115</v>
-      </c>
-      <c r="E29" s="6">
-        <v>32935.07606109668</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="8">
-        <v>1244.2215540423297</v>
-      </c>
-      <c r="E30" s="9">
-        <v>34623.067177731624</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="5">
-        <v>146.92085936757084</v>
-      </c>
-      <c r="E31" s="6">
-        <v>34323.740845060835</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="8">
-        <v>13.304259984882567</v>
-      </c>
-      <c r="E32" s="9">
-        <v>33354.88232384348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="D33" s="5">
-        <v>6624.047845462972</v>
+        <v>6624.0478454629765</v>
       </c>
       <c r="E33" s="6">
-        <v>105643.6256012702</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6525.420439999601</v>
+      </c>
+      <c r="F33" s="6">
+        <v>7322.741019654662</v>
+      </c>
+      <c r="G33" s="6">
+        <v>922.811737414687</v>
+      </c>
+      <c r="H33" s="6">
+        <v>79737.33510241697</v>
+      </c>
+      <c r="I33" s="6">
+        <v>105666.57003388379</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34" s="8">
         <v>5</v>
       </c>
       <c r="E34" s="9">
+        <v>38090.084</v>
+      </c>
+      <c r="F34" s="9">
+        <v>1178.4962454826832</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>104827.73300000001</v>
+      </c>
+      <c r="I34" s="9">
         <v>128484.40052119324</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D35" s="5">
         <v>439.3470135995009</v>
       </c>
       <c r="E35" s="6">
-        <v>124407.191937363</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13244.588362754474</v>
+      </c>
+      <c r="F35" s="6">
+        <v>2902.7384811733114</v>
+      </c>
+      <c r="G35" s="6">
+        <v>547.93558504785</v>
+      </c>
+      <c r="H35" s="6">
+        <v>98151.95016935398</v>
+      </c>
+      <c r="I35" s="6">
+        <v>124420.83553372786</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D36" s="8">
         <v>48.8</v>
       </c>
       <c r="E36" s="9">
-        <v>128892.63383999883</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>19398.326024590166</v>
+      </c>
+      <c r="F36" s="9">
+        <v>4835.941766379408</v>
+      </c>
+      <c r="G36" s="9">
+        <v>439.0079530880099</v>
+      </c>
+      <c r="H36" s="9">
+        <v>100408.9974180328</v>
+      </c>
+      <c r="I36" s="9">
+        <v>128903.56513826884</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D37" s="5">
         <v>104.82085757953837</v>
       </c>
       <c r="E37" s="6">
-        <v>122667.13772450919</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14269.268106922753</v>
+      </c>
+      <c r="F37" s="6">
+        <v>3512.927043787905</v>
+      </c>
+      <c r="G37" s="6">
+        <v>565.6513648638987</v>
+      </c>
+      <c r="H37" s="6">
+        <v>96180.05109585279</v>
+      </c>
+      <c r="I37" s="6">
+        <v>122681.22244380113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D38" s="8">
-        <v>98.89189999999999</v>
+        <v>98.8919</v>
       </c>
       <c r="E38" s="9">
-        <v>126177.97265657756</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17368.310448075114</v>
+      </c>
+      <c r="F38" s="9">
+        <v>3313.987838495827</v>
+      </c>
+      <c r="G38" s="9">
+        <v>459.4186347216037</v>
+      </c>
+      <c r="H38" s="9">
+        <v>99268.24497511427</v>
+      </c>
+      <c r="I38" s="9">
+        <v>126189.41218083136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D39" s="5">
         <v>131.02345601996257</v>
       </c>
       <c r="E39" s="6">
-        <v>123389.19081682667</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5754.698711473473</v>
+      </c>
+      <c r="F39" s="6">
+        <v>1950.1890209629553</v>
+      </c>
+      <c r="G39" s="6">
+        <v>635.8571947786459</v>
+      </c>
+      <c r="H39" s="6">
+        <v>98059.38334244152</v>
+      </c>
+      <c r="I39" s="6">
+        <v>123405.02366132155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D40" s="8">
         <v>55.8108</v>
       </c>
       <c r="E40" s="9">
-        <v>123005.50203533602</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16216.025930465074</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1573.8968098617154</v>
+      </c>
+      <c r="G40" s="9">
+        <v>560.34360358248</v>
+      </c>
+      <c r="H40" s="9">
+        <v>98121.27792459527</v>
+      </c>
+      <c r="I40" s="9">
+        <v>123019.45459136914</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D41" s="5">
         <v>7.8649000000000004</v>
       </c>
       <c r="E41" s="6">
+        <v>38783.348802909124</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
+        <v>108100.97048525728</v>
+      </c>
+      <c r="I41" s="6">
         <v>129337.135747767</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D42" s="8">
         <v>41.45302557704304</v>
       </c>
       <c r="E42" s="9">
-        <v>111681.96711526945</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7089.488545385047</v>
+      </c>
+      <c r="F42" s="9">
+        <v>2096.9769310220977</v>
+      </c>
+      <c r="G42" s="9">
+        <v>445.5310603547899</v>
+      </c>
+      <c r="H42" s="9">
+        <v>88277.3882979178</v>
+      </c>
+      <c r="I42" s="9">
+        <v>111693.06083891395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D43" s="5">
         <v>27.04678727386151</v>
       </c>
       <c r="E43" s="6">
-        <v>109514.49149685762</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6558.949061260263</v>
+      </c>
+      <c r="F43" s="6">
+        <v>2503.759352251832</v>
+      </c>
+      <c r="G43" s="6">
+        <v>682.8393425529915</v>
+      </c>
+      <c r="H43" s="6">
+        <v>86031.99832133962</v>
+      </c>
+      <c r="I43" s="6">
+        <v>109531.49419685753</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D44" s="8">
         <v>5</v>
       </c>
       <c r="E44" s="9">
+        <v>10427.814</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>89289.499</v>
+      </c>
+      <c r="I44" s="9">
         <v>110839.53368353083</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D45" s="5">
         <v>7</v>
       </c>
       <c r="E45" s="6">
-        <v>119451.84443888701</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7084.001428571429</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6">
+        <v>97373.49642857144</v>
+      </c>
+      <c r="I45" s="6">
+        <v>119451.84443888704</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D46" s="8">
-        <v>1012.0715567240103</v>
+        <v>1012.0715567240102</v>
       </c>
       <c r="E46" s="9">
-        <v>112387.74785210163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7081.5712701865605</v>
+      </c>
+      <c r="F46" s="9">
+        <v>8189.034719982412</v>
+      </c>
+      <c r="G46" s="9">
+        <v>1093.8101625162078</v>
+      </c>
+      <c r="H46" s="9">
+        <v>83530.32836837438</v>
+      </c>
+      <c r="I46" s="9">
+        <v>112414.98372574156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D47" s="5">
         <v>113.88050000000001</v>
       </c>
       <c r="E47" s="6">
-        <v>119902.66564267693</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10779.919125750235</v>
+      </c>
+      <c r="F47" s="6">
+        <v>10617.287308236353</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1007.1089504698227</v>
+      </c>
+      <c r="H47" s="6">
+        <v>87331.64381312719</v>
+      </c>
+      <c r="I47" s="6">
+        <v>119927.74265608989</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D48" s="8">
-        <v>230.82903611608126</v>
+        <v>230.8290361160812</v>
       </c>
       <c r="E48" s="9">
-        <v>112167.07194298417</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5988.333761030249</v>
+      </c>
+      <c r="F48" s="9">
+        <v>9331.575928677443</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1702.7438467959923</v>
+      </c>
+      <c r="H48" s="9">
+        <v>82291.21863163535</v>
+      </c>
+      <c r="I48" s="9">
+        <v>112209.47026569294</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D49" s="5">
-        <v>293.1846287581491</v>
+        <v>293.18462875814913</v>
       </c>
       <c r="E49" s="6">
-        <v>111061.16658090334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6298.53941464069</v>
+      </c>
+      <c r="F49" s="6">
+        <v>8026.263014948032</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1548.17341852699</v>
+      </c>
+      <c r="H49" s="6">
+        <v>82799.63584243649</v>
+      </c>
+      <c r="I49" s="6">
+        <v>111099.71609986434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D50" s="8">
         <v>198.32165963817846</v>
       </c>
       <c r="E50" s="9">
-        <v>108091.63504115636</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6151.132519863803</v>
+      </c>
+      <c r="F50" s="9">
+        <v>5116.760044286309</v>
+      </c>
+      <c r="G50" s="9">
+        <v>529.032628645854</v>
+      </c>
+      <c r="H50" s="9">
+        <v>82572.84358315052</v>
+      </c>
+      <c r="I50" s="9">
+        <v>108104.80795389652</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D51" s="5">
-        <v>172.85573221160166</v>
+        <v>172.8557322116017</v>
       </c>
       <c r="E51" s="6">
-        <v>115150.47019679256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8570.980091434572</v>
+      </c>
+      <c r="F51" s="6">
+        <v>9006.627356398716</v>
+      </c>
+      <c r="G51" s="6">
+        <v>234.0800839999879</v>
+      </c>
+      <c r="H51" s="6">
+        <v>85090.93268249527</v>
+      </c>
+      <c r="I51" s="6">
+        <v>115156.29879101101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D52" s="8">
         <v>156.09402776044917</v>
       </c>
       <c r="E52" s="9">
-        <v>103527.84207238557</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7489.928389792203</v>
+      </c>
+      <c r="F52" s="9">
+        <v>2292.6429440388692</v>
+      </c>
+      <c r="G52" s="9">
+        <v>847.3383589854574</v>
+      </c>
+      <c r="H52" s="9">
+        <v>81618.9580582289</v>
+      </c>
+      <c r="I52" s="9">
+        <v>103548.94079798387</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D53" s="5">
         <v>34.3999</v>
       </c>
       <c r="E53" s="6">
+        <v>9950.85218270983</v>
+      </c>
+      <c r="F53" s="6">
+        <v>2507.1305904836254</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>83786.70147862348</v>
+      </c>
+      <c r="I53" s="6">
         <v>106216.23846715478</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D54" s="8">
-        <v>25.240499999999997</v>
+        <v>25.2405</v>
       </c>
       <c r="E54" s="9">
-        <v>99971.39717017913</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5434.655018719914</v>
+      </c>
+      <c r="F54" s="9">
+        <v>848.7898658823872</v>
+      </c>
+      <c r="G54" s="9">
+        <v>281.9194681750564</v>
+      </c>
+      <c r="H54" s="9">
+        <v>79788.28300657672</v>
+      </c>
+      <c r="I54" s="9">
+        <v>99978.41696508961</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D55" s="5">
         <v>62.35362776044916</v>
       </c>
       <c r="E55" s="6">
-        <v>102944.27580017257</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6632.976698467894</v>
+      </c>
+      <c r="F55" s="6">
+        <v>2744.276693304838</v>
+      </c>
+      <c r="G55" s="6">
+        <v>1248.829122911728</v>
+      </c>
+      <c r="H55" s="6">
+        <v>80623.75711821631</v>
+      </c>
+      <c r="I55" s="6">
+        <v>102975.37164601043</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D56" s="8">
         <v>31.5</v>
       </c>
       <c r="E56" s="9">
-        <v>103540.48111132812</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7489.647619047618</v>
+      </c>
+      <c r="F56" s="9">
+        <v>2089.270411846903</v>
+      </c>
+      <c r="G56" s="9">
+        <v>1500.9410389539933</v>
+      </c>
+      <c r="H56" s="9">
+        <v>82067.62357142857</v>
+      </c>
+      <c r="I56" s="9">
+        <v>103577.85454401221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D57" s="5">
-        <v>92.01907449716917</v>
+        <v>92.01907449716916</v>
       </c>
       <c r="E57" s="6">
-        <v>108607.43943727268</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11906.998260819359</v>
+      </c>
+      <c r="F57" s="6">
+        <v>7115.085050658596</v>
+      </c>
+      <c r="G57" s="6">
+        <v>485.7040511398552</v>
+      </c>
+      <c r="H57" s="6">
+        <v>83112.23359351342</v>
+      </c>
+      <c r="I57" s="6">
+        <v>108619.53346840951</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D58" s="8">
-        <v>16.616200000000003</v>
+        <v>16.6162</v>
       </c>
       <c r="E58" s="9">
-        <v>111851.07811690301</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21819.201742877434</v>
+      </c>
+      <c r="F58" s="9">
+        <v>5042.832139651279</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>88035.16501479983</v>
+      </c>
+      <c r="I58" s="9">
+        <v>111851.07811690302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D59" s="5">
         <v>20.9560766687461</v>
       </c>
       <c r="E59" s="6">
-        <v>104759.73982224194</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9740.847641793536</v>
+      </c>
+      <c r="F59" s="6">
+        <v>5509.822046663021</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1163.3172643185526</v>
+      </c>
+      <c r="H59" s="6">
+        <v>80361.68718059322</v>
+      </c>
+      <c r="I59" s="6">
+        <v>104788.70642275446</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D60" s="8">
-        <v>17.746602183406118</v>
+        <v>17.746602183406115</v>
       </c>
       <c r="E60" s="9">
-        <v>111994.47454732104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9099.67036681528</v>
+      </c>
+      <c r="F60" s="9">
+        <v>10575.110771319889</v>
+      </c>
+      <c r="G60" s="9">
+        <v>291.3916066764881</v>
+      </c>
+      <c r="H60" s="9">
+        <v>82310.5416334257</v>
+      </c>
+      <c r="I60" s="9">
+        <v>112001.73019848537</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D61" s="5">
-        <v>30.586499999999997</v>
+        <v>30.5865</v>
       </c>
       <c r="E61" s="6">
-        <v>103978.697395067</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10379.405293184904</v>
+      </c>
+      <c r="F61" s="6">
+        <v>3971.1904285245714</v>
+      </c>
+      <c r="G61" s="6">
+        <v>495.1289150771894</v>
+      </c>
+      <c r="H61" s="6">
+        <v>83013.71051486494</v>
+      </c>
+      <c r="I61" s="6">
+        <v>103991.02610532097</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="8">
+        <v>6.113695645016942</v>
+      </c>
+      <c r="E62" s="9">
+        <v>8183.410314312654</v>
+      </c>
+      <c r="F62" s="9">
+        <v>23934.701568517015</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>81980.51760049928</v>
+      </c>
+      <c r="I62" s="9">
+        <v>126306.12762520669</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="5">
+        <v>4865.8938181095455</v>
+      </c>
+      <c r="E63" s="6">
+        <v>5586.744931043383</v>
+      </c>
+      <c r="F63" s="6">
+        <v>7739.598946077702</v>
+      </c>
+      <c r="G63" s="6">
+        <v>939.1026910766847</v>
+      </c>
+      <c r="H63" s="6">
+        <v>76954.96994217909</v>
+      </c>
+      <c r="I63" s="6">
+        <v>102389.39229893383</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D62" s="8">
-        <v>6.113695645016943</v>
-      </c>
-      <c r="E62" s="9">
-        <v>126306.12762520665</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="5">
-        <v>4865.893818109541</v>
-      </c>
-      <c r="E63" s="6">
-        <v>102366.05435480874</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D64" s="8">
-        <v>378.1064241952677</v>
+        <v>378.1064241952678</v>
       </c>
       <c r="E64" s="9">
-        <v>107380.4842198541</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7177.513762784259</v>
+      </c>
+      <c r="F64" s="9">
+        <v>10465.652601439839</v>
+      </c>
+      <c r="G64" s="9">
+        <v>790.761561489961</v>
+      </c>
+      <c r="H64" s="9">
+        <v>78833.18129375769</v>
+      </c>
+      <c r="I64" s="9">
+        <v>107400.17418316402</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D65" s="5">
-        <v>943.6659632607818</v>
+        <v>943.6659632607816</v>
       </c>
       <c r="E65" s="6">
-        <v>102883.89484930919</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5056.295955610809</v>
+      </c>
+      <c r="F65" s="6">
+        <v>8579.934136593623</v>
+      </c>
+      <c r="G65" s="6">
+        <v>1653.0096269116714</v>
+      </c>
+      <c r="H65" s="6">
+        <v>76463.51666111428</v>
+      </c>
+      <c r="I65" s="6">
+        <v>102925.03940484353</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D66" s="8">
-        <v>918.2556719934684</v>
+        <v>918.2556719934682</v>
       </c>
       <c r="E66" s="9">
-        <v>103421.13775323213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5465.009556165806</v>
+      </c>
+      <c r="F66" s="9">
+        <v>8840.890327437573</v>
+      </c>
+      <c r="G66" s="9">
+        <v>1507.8081260130343</v>
+      </c>
+      <c r="H66" s="9">
+        <v>76872.80661092953</v>
+      </c>
+      <c r="I66" s="9">
+        <v>103458.45574909945</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D67" s="5">
-        <v>2017.929482882685</v>
+        <v>2017.9294828826846</v>
       </c>
       <c r="E67" s="6">
-        <v>100091.13482442997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5295.956580514854</v>
+      </c>
+      <c r="F67" s="6">
+        <v>6035.886715119854</v>
+      </c>
+      <c r="G67" s="6">
+        <v>509.8711862964077</v>
+      </c>
+      <c r="H67" s="6">
+        <v>76592.77979827224</v>
+      </c>
+      <c r="I67" s="6">
+        <v>100103.83061724552</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D68" s="8">
-        <v>594.4027956822614</v>
+        <v>594.4027956822613</v>
       </c>
       <c r="E68" s="9">
-        <v>104462.66142060905</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6523.612472989135</v>
+      </c>
+      <c r="F68" s="9">
+        <v>8860.3947917996</v>
+      </c>
+      <c r="G68" s="9">
+        <v>500.09113295758544</v>
+      </c>
+      <c r="H68" s="9">
+        <v>77816.9724497571</v>
+      </c>
+      <c r="I68" s="9">
+        <v>104475.11369009088</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D69" s="5">
         <v>13.533480095053402</v>
       </c>
       <c r="E69" s="6">
+        <v>8600.354626606199</v>
+      </c>
+      <c r="F69" s="6">
+        <v>3067.170516058564</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
+        <v>80468.35821152943</v>
+      </c>
+      <c r="I69" s="6">
         <v>101694.03064080491</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D70" s="8">
-        <v>1799.200816803707</v>
+        <v>1799.2008168037055</v>
       </c>
       <c r="E70" s="9">
-        <v>33041.489520151765</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1064.8686222970748</v>
+      </c>
+      <c r="F70" s="9">
+        <v>1696.3862621474843</v>
+      </c>
+      <c r="G70" s="9">
+        <v>158.43212878312076</v>
+      </c>
+      <c r="H70" s="9">
+        <v>27269.470205486326</v>
+      </c>
+      <c r="I70" s="9">
+        <v>33046.0717709053</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D71" s="5">
-        <v>1799.200816803707</v>
+        <v>1799.2008168037055</v>
       </c>
       <c r="E71" s="6">
-        <v>33041.489520151765</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1064.8686222970748</v>
+      </c>
+      <c r="F71" s="6">
+        <v>1696.3862621474843</v>
+      </c>
+      <c r="G71" s="6">
+        <v>158.43212878312076</v>
+      </c>
+      <c r="H71" s="6">
+        <v>27269.470205486326</v>
+      </c>
+      <c r="I71" s="6">
+        <v>33046.0717709053</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D72" s="8">
-        <v>503.927720575899</v>
+        <v>503.92772057589895</v>
       </c>
       <c r="E72" s="9">
-        <v>33124.847711875685</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1609.1418171818523</v>
+      </c>
+      <c r="F72" s="9">
+        <v>1105.7455629905667</v>
+      </c>
+      <c r="G72" s="9">
+        <v>5.891537959651315</v>
+      </c>
+      <c r="H72" s="9">
+        <v>27763.53151680664</v>
+      </c>
+      <c r="I72" s="9">
+        <v>33125.02092309375</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="5">
+        <v>268.17236507870393</v>
+      </c>
+      <c r="E73" s="6">
+        <v>603.7223166684781</v>
+      </c>
+      <c r="F73" s="6">
+        <v>1761.4704168841688</v>
+      </c>
+      <c r="G73" s="6">
+        <v>514.9486769031606</v>
+      </c>
+      <c r="H73" s="6">
+        <v>25833.834995575307</v>
+      </c>
+      <c r="I73" s="6">
+        <v>30674.206745087176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="8">
+        <v>307.8129951260264</v>
+      </c>
+      <c r="E74" s="9">
+        <v>1190.055731597358</v>
+      </c>
+      <c r="F74" s="9">
+        <v>1931.4526522695144</v>
+      </c>
+      <c r="G74" s="9">
+        <v>96.24509396829758</v>
+      </c>
+      <c r="H74" s="9">
+        <v>27274.180682712413</v>
+      </c>
+      <c r="I74" s="9">
+        <v>33555.9522900806</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="5">
+        <v>494.0422081864349</v>
+      </c>
+      <c r="E75" s="6">
+        <v>633.4811595662976</v>
+      </c>
+      <c r="F75" s="6">
+        <v>1876.2300757134435</v>
+      </c>
+      <c r="G75" s="6">
+        <v>150.12513702508252</v>
+      </c>
+      <c r="H75" s="6">
+        <v>27553.579078431314</v>
+      </c>
+      <c r="I75" s="6">
+        <v>33762.73099343576</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="8">
+        <v>211.84065703191092</v>
+      </c>
+      <c r="E76" s="9">
+        <v>1159.7402179618273</v>
+      </c>
+      <c r="F76" s="9">
+        <v>2337.945945394533</v>
+      </c>
+      <c r="G76" s="9">
+        <v>189.73532919977794</v>
+      </c>
+      <c r="H76" s="9">
+        <v>27237.05698255386</v>
+      </c>
+      <c r="I76" s="9">
+        <v>33506.570968142056</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="5">
+        <v>13.404870804741108</v>
+      </c>
+      <c r="E77" s="6">
+        <v>1354.6199718415608</v>
+      </c>
+      <c r="F77" s="6">
+        <v>433.4945901610585</v>
+      </c>
+      <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
+        <v>27350.12869098211</v>
+      </c>
+      <c r="I77" s="6">
+        <v>32130.2688551638</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="5">
-        <v>268.1723650787039</v>
-      </c>
-      <c r="E73" s="6">
-        <v>30659.464492397667</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="8">
-        <v>307.81299512602607</v>
-      </c>
-      <c r="E74" s="9">
-        <v>33553.14001531323</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="5">
-        <v>494.0422081864352</v>
-      </c>
-      <c r="E75" s="6">
-        <v>33758.36640612935</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="7" t="s">
+      <c r="C78" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="8">
+        <v>7074.141641725853</v>
+      </c>
+      <c r="E78" s="9">
+        <v>2646.555248761773</v>
+      </c>
+      <c r="F78" s="9">
+        <v>5530.240958845777</v>
+      </c>
+      <c r="G78" s="9">
+        <v>1028.8518396293905</v>
+      </c>
+      <c r="H78" s="9">
+        <v>34025.76831456796</v>
+      </c>
+      <c r="I78" s="9">
+        <v>45515.60615571737</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="5">
+        <v>7074.141641725853</v>
+      </c>
+      <c r="E79" s="6">
+        <v>2646.555248761773</v>
+      </c>
+      <c r="F79" s="6">
+        <v>5530.240958845777</v>
+      </c>
+      <c r="G79" s="6">
+        <v>1028.8518396293905</v>
+      </c>
+      <c r="H79" s="6">
+        <v>34025.76831456796</v>
+      </c>
+      <c r="I79" s="6">
+        <v>45515.60615571737</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="8">
-        <v>211.84065703191084</v>
-      </c>
-      <c r="E76" s="9">
-        <v>33500.99274939744</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C77" s="4" t="s">
+      <c r="D80" s="8">
+        <v>755.6338129537697</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1705.7967352622795</v>
+      </c>
+      <c r="F80" s="9">
+        <v>4848.987120321878</v>
+      </c>
+      <c r="G80" s="9">
+        <v>681.2721593343047</v>
+      </c>
+      <c r="H80" s="9">
+        <v>32827.36814829141</v>
+      </c>
+      <c r="I80" s="9">
+        <v>43388.78506058021</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D77" s="5">
-        <v>13.404870804741112</v>
-      </c>
-      <c r="E77" s="6">
-        <v>32130.26885516379</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="8">
-        <v>7074.1416417258615</v>
-      </c>
-      <c r="E78" s="9">
-        <v>45490.049126531616</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="5">
-        <v>7074.1416417258615</v>
-      </c>
-      <c r="E79" s="6">
-        <v>45490.049126531616</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="8">
-        <v>755.63381295377</v>
-      </c>
-      <c r="E80" s="9">
-        <v>43371.89796051253</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="D81" s="5">
-        <v>1400.1228422882546</v>
+        <v>1400.1228422882543</v>
       </c>
       <c r="E81" s="6">
-        <v>43778.2728816326</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2204.336975779418</v>
+      </c>
+      <c r="F81" s="6">
+        <v>4452.484044723536</v>
+      </c>
+      <c r="G81" s="6">
+        <v>669.7367868063678</v>
+      </c>
+      <c r="H81" s="6">
+        <v>33549.9316851332</v>
+      </c>
+      <c r="I81" s="6">
+        <v>43794.92152378963</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D82" s="8">
-        <v>1501.9820026028483</v>
+        <v>1501.9820026028494</v>
       </c>
       <c r="E82" s="9">
-        <v>44641.24868850295</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2770.1636222579245</v>
+      </c>
+      <c r="F82" s="9">
+        <v>5056.700953024536</v>
+      </c>
+      <c r="G82" s="9">
+        <v>954.1548302871668</v>
+      </c>
+      <c r="H82" s="9">
+        <v>33743.91977460237</v>
+      </c>
+      <c r="I82" s="9">
+        <v>44664.935593985814</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D83" s="5">
-        <v>2082.044737587798</v>
+        <v>2082.0447375877966</v>
       </c>
       <c r="E83" s="6">
-        <v>47754.21476766426</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3183.3134758562464</v>
+      </c>
+      <c r="F83" s="6">
+        <v>6496.280715805925</v>
+      </c>
+      <c r="G83" s="6">
+        <v>1732.3254303627489</v>
+      </c>
+      <c r="H83" s="6">
+        <v>35065.73243921159</v>
+      </c>
+      <c r="I83" s="6">
+        <v>47797.317238411</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D84" s="8">
-        <v>1300.6189175504553</v>
+        <v>1300.618917550454</v>
       </c>
       <c r="E84" s="9">
-        <v>45954.142533550774</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2671.57163839263</v>
+      </c>
+      <c r="F84" s="9">
+        <v>6121.660510665643</v>
+      </c>
+      <c r="G84" s="9">
+        <v>595.2417230808304</v>
+      </c>
+      <c r="H84" s="9">
+        <v>33892.12659284368</v>
+      </c>
+      <c r="I84" s="9">
+        <v>45968.83916021571</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D85" s="5">
         <v>33.73932874295496</v>
       </c>
       <c r="E85" s="6">
-        <v>44139.21674625726</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2477.0161277001353</v>
+      </c>
+      <c r="F85" s="6">
+        <v>4180.766160819598</v>
+      </c>
+      <c r="G85" s="6">
+        <v>345.3688902199999</v>
+      </c>
+      <c r="H85" s="6">
+        <v>34134.77979254601</v>
+      </c>
+      <c r="I85" s="6">
+        <v>44147.816431811065</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D86" s="8">
-        <v>3492.8650885237334</v>
+        <v>3492.865088523731</v>
       </c>
       <c r="E86" s="9">
-        <v>45659.08518864112</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2564.91665634949</v>
+      </c>
+      <c r="F86" s="9">
+        <v>2257.3867934385103</v>
+      </c>
+      <c r="G86" s="9">
+        <v>795.0911345325327</v>
+      </c>
+      <c r="H86" s="9">
+        <v>36936.30446321048</v>
+      </c>
+      <c r="I86" s="9">
+        <v>45678.78669228206</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D87" s="5">
-        <v>3492.8650885237334</v>
+        <v>3492.865088523731</v>
       </c>
       <c r="E87" s="6">
-        <v>45659.08518864112</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2564.91665634949</v>
+      </c>
+      <c r="F87" s="6">
+        <v>2257.3867934385103</v>
+      </c>
+      <c r="G87" s="6">
+        <v>795.0911345325327</v>
+      </c>
+      <c r="H87" s="6">
+        <v>36936.30446321048</v>
+      </c>
+      <c r="I87" s="6">
+        <v>45678.78669228206</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D88" s="8">
-        <v>432.1519574329623</v>
+        <v>432.1519574329622</v>
       </c>
       <c r="E88" s="9">
-        <v>43959.18631321879</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1707.9433715494608</v>
+      </c>
+      <c r="F88" s="9">
+        <v>1827.7587066563974</v>
+      </c>
+      <c r="G88" s="9">
+        <v>460.3852534637851</v>
+      </c>
+      <c r="H88" s="9">
+        <v>35912.4457718174</v>
+      </c>
+      <c r="I88" s="9">
+        <v>43970.64990627976</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="5">
+        <v>1079.9836222042031</v>
+      </c>
+      <c r="E89" s="6">
+        <v>2119.2669792402526</v>
+      </c>
+      <c r="F89" s="6">
+        <v>2465.4125943572285</v>
+      </c>
+      <c r="G89" s="6">
+        <v>826.996737905761</v>
+      </c>
+      <c r="H89" s="6">
+        <v>36238.74439237061</v>
+      </c>
+      <c r="I89" s="6">
+        <v>45107.863609209024</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="8">
+        <v>645.7555828556582</v>
+      </c>
+      <c r="E90" s="9">
+        <v>2471.0125782853947</v>
+      </c>
+      <c r="F90" s="9">
+        <v>2106.595948172259</v>
+      </c>
+      <c r="G90" s="9">
+        <v>928.3851285997591</v>
+      </c>
+      <c r="H90" s="9">
+        <v>36636.28066776207</v>
+      </c>
+      <c r="I90" s="9">
+        <v>45211.13153259323</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="5">
+        <v>671.429541954395</v>
+      </c>
+      <c r="E91" s="6">
+        <v>3328.046438260475</v>
+      </c>
+      <c r="F91" s="6">
+        <v>2460.2947060062547</v>
+      </c>
+      <c r="G91" s="6">
+        <v>1270.526533938705</v>
+      </c>
+      <c r="H91" s="6">
+        <v>38128.23692203522</v>
+      </c>
+      <c r="I91" s="6">
+        <v>47268.44702062443</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="8">
+        <v>663.5443840764897</v>
+      </c>
+      <c r="E92" s="9">
+        <v>3167.5715010767503</v>
+      </c>
+      <c r="F92" s="9">
+        <v>2140.0409492031454</v>
+      </c>
+      <c r="G92" s="9">
+        <v>350.3425272115832</v>
+      </c>
+      <c r="H92" s="9">
+        <v>37824.352617642595</v>
+      </c>
+      <c r="I92" s="9">
+        <v>46567.059237623595</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="5">
-        <v>1079.9836222042027</v>
-      </c>
-      <c r="E89" s="6">
-        <v>45087.33165568534</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D90" s="8">
-        <v>645.7555828556583</v>
-      </c>
-      <c r="E90" s="9">
-        <v>45188.20306172408</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="5">
-        <v>671.4295419543947</v>
-      </c>
-      <c r="E91" s="6">
-        <v>47236.87703239129</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C92" s="7" t="s">
+      <c r="C93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="5">
+        <v>6412.859666996452</v>
+      </c>
+      <c r="E93" s="6">
+        <v>2620.9330093100443</v>
+      </c>
+      <c r="F93" s="6">
+        <v>693.9782916249696</v>
+      </c>
+      <c r="G93" s="6">
+        <v>227.966061718056</v>
+      </c>
+      <c r="H93" s="6">
+        <v>33193.1021146321</v>
+      </c>
+      <c r="I93" s="6">
+        <v>40264.395306772756</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="8">
+        <v>4923.225815726959</v>
+      </c>
+      <c r="E94" s="9">
+        <v>2579.418690395841</v>
+      </c>
+      <c r="F94" s="9">
+        <v>709.6451441094069</v>
+      </c>
+      <c r="G94" s="9">
+        <v>218.3415965747867</v>
+      </c>
+      <c r="H94" s="9">
+        <v>32832.86228910882</v>
+      </c>
+      <c r="I94" s="9">
+        <v>39842.96668282923</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="8">
-        <v>663.5443840764891</v>
-      </c>
-      <c r="E92" s="9">
-        <v>46558.49418023098</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D93" s="5">
-        <v>6412.859666996459</v>
-      </c>
-      <c r="E93" s="6">
-        <v>40258.72179990326</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" s="8">
-        <v>4923.225815726957</v>
-      </c>
-      <c r="E94" s="9">
-        <v>39837.53368693193</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="D95" s="5">
-        <v>720.9342325402239</v>
+        <v>720.9342325402241</v>
       </c>
       <c r="E95" s="6">
-        <v>38593.136761251786</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2083.1170619012123</v>
+      </c>
+      <c r="F95" s="6">
+        <v>301.50846997449486</v>
+      </c>
+      <c r="G95" s="6">
+        <v>198.15043843302968</v>
+      </c>
+      <c r="H95" s="6">
+        <v>32166.626975960415</v>
+      </c>
+      <c r="I95" s="6">
+        <v>38598.0707072762</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C96" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="8">
+        <v>1258.1415106646107</v>
+      </c>
+      <c r="E96" s="9">
+        <v>2022.1820663925512</v>
+      </c>
+      <c r="F96" s="9">
+        <v>477.2474602362671</v>
+      </c>
+      <c r="G96" s="9">
+        <v>230.76123881808124</v>
+      </c>
+      <c r="H96" s="9">
+        <v>31966.028773038757</v>
+      </c>
+      <c r="I96" s="9">
+        <v>38562.693827090545</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="5">
+        <v>991.7349020621762</v>
+      </c>
+      <c r="E97" s="6">
+        <v>2218.754118433671</v>
+      </c>
+      <c r="F97" s="6">
+        <v>610.1962739651841</v>
+      </c>
+      <c r="G97" s="6">
+        <v>192.69481135725084</v>
+      </c>
+      <c r="H97" s="6">
+        <v>32248.58511906481</v>
+      </c>
+      <c r="I97" s="6">
+        <v>39037.43319759224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="8">
+        <v>1169.334564842113</v>
+      </c>
+      <c r="E98" s="9">
+        <v>3578.728490107745</v>
+      </c>
+      <c r="F98" s="9">
+        <v>1296.1882420379636</v>
+      </c>
+      <c r="G98" s="9">
+        <v>286.93464452282774</v>
+      </c>
+      <c r="H98" s="9">
+        <v>34533.72498755756</v>
+      </c>
+      <c r="I98" s="9">
+        <v>42497.30804191483</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="5">
+        <v>770.2154813508923</v>
+      </c>
+      <c r="E99" s="6">
+        <v>2897.859392447812</v>
+      </c>
+      <c r="F99" s="6">
+        <v>720.7074292595104</v>
+      </c>
+      <c r="G99" s="6">
+        <v>149.4860753421215</v>
+      </c>
+      <c r="H99" s="6">
+        <v>33030.42078930391</v>
+      </c>
+      <c r="I99" s="6">
+        <v>40105.05633279473</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="8">
+        <v>12.865124266925012</v>
+      </c>
+      <c r="E100" s="9">
+        <v>2794.8505091533916</v>
+      </c>
+      <c r="F100" s="9">
+        <v>0</v>
+      </c>
+      <c r="G100" s="9">
+        <v>0</v>
+      </c>
+      <c r="H100" s="9">
+        <v>33557.2219398417</v>
+      </c>
+      <c r="I100" s="9">
+        <v>39955.64477244145</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="8">
-        <v>1258.1415106646102</v>
-      </c>
-      <c r="E96" s="9">
-        <v>38556.95832790239</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="5">
-        <v>991.7349020621771</v>
-      </c>
-      <c r="E97" s="6">
-        <v>39032.635096684884</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D98" s="8">
-        <v>1169.3345648421132</v>
-      </c>
-      <c r="E98" s="9">
-        <v>42490.16773928289</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C99" s="4" t="s">
+      <c r="D101" s="5">
+        <v>1051.6118238374104</v>
+      </c>
+      <c r="E101" s="6">
+        <v>3498.8615748232924</v>
+      </c>
+      <c r="F101" s="6">
+        <v>723.7620287503598</v>
+      </c>
+      <c r="G101" s="6">
+        <v>320.6282132944231</v>
+      </c>
+      <c r="H101" s="6">
+        <v>36014.466551886806</v>
+      </c>
+      <c r="I101" s="6">
+        <v>43700.70743006929</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="D99" s="5">
-        <v>770.2154813508924</v>
-      </c>
-      <c r="E99" s="6">
-        <v>40101.3341294376</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D100" s="8">
-        <v>12.865124266925008</v>
-      </c>
-      <c r="E100" s="9">
-        <v>39955.64477244147</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" s="5">
-        <v>1051.611823837411</v>
-      </c>
-      <c r="E101" s="6">
-        <v>43692.72378738431</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="D102" s="8">
         <v>9.5</v>
       </c>
       <c r="E102" s="9">
-        <v>42538.299750952174</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2854.0505263157893</v>
+      </c>
+      <c r="F102" s="9">
+        <v>0</v>
+      </c>
+      <c r="G102" s="9">
+        <v>284.52009871043657</v>
+      </c>
+      <c r="H102" s="9">
+        <v>35798.7323486842</v>
+      </c>
+      <c r="I102" s="9">
+        <v>42545.38430156439</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="5">
+        <v>241.73200014257563</v>
+      </c>
+      <c r="E103" s="6">
+        <v>2788.625481588066</v>
+      </c>
+      <c r="F103" s="6">
+        <v>660.7876093485844</v>
+      </c>
+      <c r="G103" s="6">
+        <v>177.4432231607853</v>
+      </c>
+      <c r="H103" s="6">
+        <v>34765.40326265113</v>
+      </c>
+      <c r="I103" s="6">
+        <v>42131.23875687391</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="8">
+        <v>323.82954881985154</v>
+      </c>
+      <c r="E104" s="9">
+        <v>2560.3812828131818</v>
+      </c>
+      <c r="F104" s="9">
+        <v>817.706266393231</v>
+      </c>
+      <c r="G104" s="9">
+        <v>398.2863422299046</v>
+      </c>
+      <c r="H104" s="9">
+        <v>34824.315011901555</v>
+      </c>
+      <c r="I104" s="9">
+        <v>42397.21813560887</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="5">
+        <v>335.4499640706868</v>
+      </c>
+      <c r="E105" s="6">
+        <v>4679.71521217498</v>
+      </c>
+      <c r="F105" s="6">
+        <v>914.7465404999253</v>
+      </c>
+      <c r="G105" s="6">
+        <v>458.41093550825985</v>
+      </c>
+      <c r="H105" s="6">
+        <v>37780.76441947241</v>
+      </c>
+      <c r="I105" s="6">
+        <v>45983.47881202855</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="8">
+        <v>133.51921080429443</v>
+      </c>
+      <c r="E106" s="9">
+        <v>4107.177446848374</v>
+      </c>
+      <c r="F106" s="9">
+        <v>222.69492879926128</v>
+      </c>
+      <c r="G106" s="9">
+        <v>64.4255766129901</v>
+      </c>
+      <c r="H106" s="9">
+        <v>36678.73024011484</v>
+      </c>
+      <c r="I106" s="9">
+        <v>44019.493272724445</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" s="5">
+        <v>7.5811</v>
+      </c>
+      <c r="E107" s="6">
+        <v>4076.7434804975537</v>
+      </c>
+      <c r="F107" s="6">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6">
+        <v>29.930152072214106</v>
+      </c>
+      <c r="H107" s="6">
+        <v>37095.80814148563</v>
+      </c>
+      <c r="I107" s="6">
+        <v>44248.79533069785</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="D103" s="5">
-        <v>241.73200014257569</v>
-      </c>
-      <c r="E103" s="6">
-        <v>42126.82042052096</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D104" s="8">
-        <v>323.82954881985165</v>
-      </c>
-      <c r="E104" s="9">
-        <v>42387.300805471314</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D105" s="5">
-        <v>335.44996407068703</v>
-      </c>
-      <c r="E105" s="6">
-        <v>45972.06437948576</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="8">
-        <v>133.5192108042944</v>
-      </c>
-      <c r="E106" s="9">
-        <v>44017.88907583184</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D107" s="5">
-        <v>7.581099999999999</v>
-      </c>
-      <c r="E107" s="6">
-        <v>44248.05006989503</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>6</v>
       </c>
       <c r="D108" s="8">
         <v>262.5275285711401</v>
       </c>
       <c r="E108" s="9">
-        <v>36655.24415243641</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>352.58714180303843</v>
+      </c>
+      <c r="F108" s="9">
+        <v>529.6045712686856</v>
+      </c>
+      <c r="G108" s="9">
+        <v>126.70570426865326</v>
+      </c>
+      <c r="H108" s="9">
+        <v>30314.325637259746</v>
+      </c>
+      <c r="I108" s="9">
+        <v>36658.39912454143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D109" s="5">
         <v>40.919</v>
       </c>
       <c r="E109" s="6">
-        <v>35577.876291994944</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>81.28473325350083</v>
+      </c>
+      <c r="F109" s="6">
+        <v>121.71002072300821</v>
+      </c>
+      <c r="G109" s="6">
+        <v>45.53592041250274</v>
+      </c>
+      <c r="H109" s="6">
+        <v>29767.71061374301</v>
+      </c>
+      <c r="I109" s="6">
+        <v>35579.010136437915</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D110" s="8">
-        <v>52.41140704899688</v>
+        <v>52.41140704899687</v>
       </c>
       <c r="E110" s="9">
-        <v>36144.25519568933</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>295.1168623567041</v>
+      </c>
+      <c r="F110" s="9">
+        <v>327.0733817263153</v>
+      </c>
+      <c r="G110" s="9">
+        <v>111.35035725758749</v>
+      </c>
+      <c r="H110" s="9">
+        <v>30054.964685980784</v>
+      </c>
+      <c r="I110" s="9">
+        <v>36147.027819645446</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D111" s="5">
-        <v>52.28211285090456</v>
+        <v>52.282112850904554</v>
       </c>
       <c r="E111" s="6">
-        <v>35921.35799900871</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>157.6151765633966</v>
+      </c>
+      <c r="F111" s="6">
+        <v>411.8665531281528</v>
+      </c>
+      <c r="G111" s="6">
+        <v>161.92207873820897</v>
+      </c>
+      <c r="H111" s="6">
+        <v>29763.495138303813</v>
+      </c>
+      <c r="I111" s="6">
+        <v>35925.389858857125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D112" s="8">
-        <v>77.55766968184655</v>
+        <v>77.55766968184653</v>
       </c>
       <c r="E112" s="9">
-        <v>38405.369363438214</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>601.8463116784944</v>
+      </c>
+      <c r="F112" s="9">
+        <v>1176.976370847587</v>
+      </c>
+      <c r="G112" s="9">
+        <v>220.46554321932618</v>
+      </c>
+      <c r="H112" s="9">
+        <v>31229.866415735327</v>
+      </c>
+      <c r="I112" s="9">
+        <v>38410.858955583964</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D113" s="5">
         <v>39.3573389893921</v>
       </c>
       <c r="E113" s="6">
-        <v>35981.925038061185</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>478.99577408152203</v>
+      </c>
+      <c r="F113" s="6">
+        <v>104.08103378231299</v>
+      </c>
+      <c r="G113" s="6">
+        <v>0</v>
+      </c>
+      <c r="H113" s="6">
+        <v>30155.569618885867</v>
+      </c>
+      <c r="I113" s="6">
+        <v>35981.92503806119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="8">
+        <v>175.49449886106208</v>
+      </c>
+      <c r="E114" s="9">
+        <v>1918.0479636972505</v>
+      </c>
+      <c r="F114" s="9">
+        <v>321.8882456213602</v>
+      </c>
+      <c r="G114" s="9">
+        <v>94.1865544800217</v>
+      </c>
+      <c r="H114" s="9">
+        <v>30699.120128674327</v>
+      </c>
+      <c r="I114" s="9">
+        <v>36889.90256506375</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D114" s="8">
-        <v>175.49449886106206</v>
-      </c>
-      <c r="E114" s="9">
-        <v>36887.5573198061</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="B115" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D115" s="5">
         <v>14.456744321623258</v>
       </c>
       <c r="E115" s="6">
+        <v>1397.6860592171831</v>
+      </c>
+      <c r="F115" s="6">
+        <v>19.669191161976798</v>
+      </c>
+      <c r="G115" s="6">
+        <v>0</v>
+      </c>
+      <c r="H115" s="6">
+        <v>29964.77856473401</v>
+      </c>
+      <c r="I115" s="6">
         <v>35684.896497178044</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="8">
+        <v>62.093125453805904</v>
+      </c>
+      <c r="E116" s="9">
+        <v>1328.1287493739728</v>
+      </c>
+      <c r="F116" s="9">
+        <v>57.71595588537733</v>
+      </c>
+      <c r="G116" s="9">
+        <v>33.44702539486085</v>
+      </c>
+      <c r="H116" s="9">
+        <v>29550.445543640824</v>
+      </c>
+      <c r="I116" s="9">
+        <v>35230.36390694957</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C116" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="8">
-        <v>62.09312545380591</v>
-      </c>
-      <c r="E116" s="9">
-        <v>35229.53107599909</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="B117" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="5">
+        <v>87.73247823401717</v>
+      </c>
+      <c r="E117" s="6">
+        <v>2447.3723465797693</v>
+      </c>
+      <c r="F117" s="6">
+        <v>593.6861218432302</v>
+      </c>
+      <c r="G117" s="6">
+        <v>164.73251553970206</v>
+      </c>
+      <c r="H117" s="6">
+        <v>31732.61269919471</v>
+      </c>
+      <c r="I117" s="6">
+        <v>38420.93633189518</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D117" s="5">
-        <v>87.73247823401721</v>
-      </c>
-      <c r="E117" s="6">
-        <v>38416.83449216886</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B118" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D118" s="8">
         <v>7.455334670467874</v>
       </c>
       <c r="E118" s="9">
+        <v>1678.3243882483894</v>
+      </c>
+      <c r="F118" s="9">
+        <v>71.88745491760554</v>
+      </c>
+      <c r="G118" s="9">
+        <v>0</v>
+      </c>
+      <c r="H118" s="9">
+        <v>29855.31957257726</v>
+      </c>
+      <c r="I118" s="9">
         <v>35618.1862511471</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D119" s="5">
-        <v>34554.22857642909</v>
+        <v>34554.22857642907</v>
       </c>
       <c r="E119" s="6">
-        <v>47877.54229342967</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3736.743103893825</v>
+      </c>
+      <c r="F119" s="6">
+        <v>3597.964789662102</v>
+      </c>
+      <c r="G119" s="6">
+        <v>700.2862895718345</v>
+      </c>
+      <c r="H119" s="6">
+        <v>37656.250608579576</v>
+      </c>
+      <c r="I119" s="6">
+        <v>47897.42994777376</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D120" s="8">
-        <v>34554.22857642909</v>
+        <v>34554.22857642907</v>
       </c>
       <c r="E120" s="9">
-        <v>47877.54229342967</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3736.743103893825</v>
+      </c>
+      <c r="F120" s="9">
+        <v>3597.964789662102</v>
+      </c>
+      <c r="G120" s="9">
+        <v>700.2862895718345</v>
+      </c>
+      <c r="H120" s="9">
+        <v>37656.250608579576</v>
+      </c>
+      <c r="I120" s="9">
+        <v>47897.42994777376</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D121" s="5">
-        <v>3601.4959073156715</v>
+        <v>3601.4959073156756</v>
       </c>
       <c r="E121" s="6">
-        <v>46401.97662990885</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3214.677204804681</v>
+      </c>
+      <c r="F121" s="6">
+        <v>2762.365800790266</v>
+      </c>
+      <c r="G121" s="6">
+        <v>465.8493975933831</v>
+      </c>
+      <c r="H121" s="6">
+        <v>37165.95902320526</v>
+      </c>
+      <c r="I121" s="6">
+        <v>46414.752049189745</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D122" s="8">
-        <v>8324.578691714018</v>
+        <v>8324.578691713994</v>
       </c>
       <c r="E122" s="9">
-        <v>46132.732386026066</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3197.245367283207</v>
+      </c>
+      <c r="F122" s="9">
+        <v>2893.2074712275253</v>
+      </c>
+      <c r="G122" s="9">
+        <v>249.5249790484524</v>
+      </c>
+      <c r="H122" s="9">
+        <v>36796.46505731522</v>
+      </c>
+      <c r="I122" s="9">
+        <v>46139.863906150866</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D123" s="5">
-        <v>7409.458439026051</v>
+        <v>7409.458439026048</v>
       </c>
       <c r="E123" s="6">
-        <v>46782.363643250836</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3416.917475920088</v>
+      </c>
+      <c r="F123" s="6">
+        <v>3191.901603247519</v>
+      </c>
+      <c r="G123" s="6">
+        <v>758.0387326365972</v>
+      </c>
+      <c r="H123" s="6">
+        <v>37092.9546990463</v>
+      </c>
+      <c r="I123" s="6">
+        <v>46803.78329379645</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D124" s="8">
-        <v>10722.075258774086</v>
+        <v>10722.075258774066</v>
       </c>
       <c r="E124" s="9">
-        <v>49773.30356705853</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4351.430558428092</v>
+      </c>
+      <c r="F124" s="9">
+        <v>4315.387626872539</v>
+      </c>
+      <c r="G124" s="9">
+        <v>1121.8730055809704</v>
+      </c>
+      <c r="H124" s="9">
+        <v>38606.54967071723</v>
+      </c>
+      <c r="I124" s="9">
+        <v>49805.55487084922</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D125" s="5">
-        <v>4056.0620960678793</v>
+        <v>4056.0620960678807</v>
       </c>
       <c r="E125" s="6">
-        <v>49323.600757917484</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4303.203025690009</v>
+      </c>
+      <c r="F125" s="6">
+        <v>4349.133564733399</v>
+      </c>
+      <c r="G125" s="6">
+        <v>639.4254754215116</v>
+      </c>
+      <c r="H125" s="6">
+        <v>38242.15687303075</v>
+      </c>
+      <c r="I125" s="6">
+        <v>49341.3528121047</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D126" s="8">
         <v>440.55818352961217</v>
       </c>
       <c r="E126" s="9">
-        <v>51876.86373871674</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3402.445588072235</v>
+      </c>
+      <c r="F126" s="9">
+        <v>6198.923281416016</v>
+      </c>
+      <c r="G126" s="9">
+        <v>462.81010896111223</v>
+      </c>
+      <c r="H126" s="9">
+        <v>38862.00052858179</v>
+      </c>
+      <c r="I126" s="9">
+        <v>51888.92271862158</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D127" s="5">
         <v>1968.0323110662916</v>
       </c>
       <c r="E127" s="6">
-        <v>64891.51588321535</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10723.883688953596</v>
+      </c>
+      <c r="F127" s="6">
+        <v>9.89179680813668</v>
+      </c>
+      <c r="G127" s="6">
+        <v>139.13989316376177</v>
+      </c>
+      <c r="H127" s="6">
+        <v>54220.726693382945</v>
+      </c>
+      <c r="I127" s="6">
+        <v>64894.98046663054</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D128" s="8">
         <v>1968.0323110662916</v>
       </c>
       <c r="E128" s="9">
-        <v>64891.51588321535</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10723.883688953596</v>
+      </c>
+      <c r="F128" s="9">
+        <v>9.89179680813668</v>
+      </c>
+      <c r="G128" s="9">
+        <v>139.13989316376177</v>
+      </c>
+      <c r="H128" s="9">
+        <v>54220.726693382945</v>
+      </c>
+      <c r="I128" s="9">
+        <v>64894.98046663054</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D129" s="5">
-        <v>189.49746903113467</v>
+        <v>189.4974690311347</v>
       </c>
       <c r="E129" s="6">
-        <v>67532.11890162107</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7024.239093036659</v>
+      </c>
+      <c r="F129" s="6">
+        <v>0</v>
+      </c>
+      <c r="G129" s="6">
+        <v>0</v>
+      </c>
+      <c r="H129" s="6">
+        <v>56403.675441852356</v>
+      </c>
+      <c r="I129" s="6">
+        <v>67532.11890162103</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D130" s="8">
         <v>414.50320431315157</v>
       </c>
       <c r="E130" s="9">
-        <v>64277.44029614752</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10262.792263214347</v>
+      </c>
+      <c r="F130" s="9">
+        <v>43.20200534658441</v>
+      </c>
+      <c r="G130" s="9">
+        <v>252.00157901222315</v>
+      </c>
+      <c r="H130" s="9">
+        <v>53618.208249617564</v>
+      </c>
+      <c r="I130" s="9">
+        <v>64283.71513560155</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D131" s="5">
         <v>409.75224682105517</v>
       </c>
       <c r="E131" s="6">
-        <v>65421.4914917772</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11041.52388449458</v>
+      </c>
+      <c r="F131" s="6">
+        <v>0</v>
+      </c>
+      <c r="G131" s="6">
+        <v>18.68049963401451</v>
+      </c>
+      <c r="H131" s="6">
+        <v>54673.35062394048</v>
+      </c>
+      <c r="I131" s="6">
+        <v>65421.95663622823</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D132" s="8">
-        <v>646.8724778587026</v>
+        <v>646.8724778587025</v>
       </c>
       <c r="E132" s="9">
-        <v>63990.52529448262</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11830.582941181498</v>
+      </c>
+      <c r="F132" s="9">
+        <v>1.4364405189657667</v>
+      </c>
+      <c r="G132" s="9">
+        <v>101.03712466586335</v>
+      </c>
+      <c r="H132" s="9">
+        <v>53515.24648609239</v>
+      </c>
+      <c r="I132" s="9">
+        <v>63993.04111894164</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D133" s="5">
-        <v>271.3838778977632</v>
+        <v>271.38387789776317</v>
       </c>
       <c r="E133" s="6">
-        <v>64707.50954764828</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11016.735861981879</v>
+      </c>
+      <c r="F133" s="6">
+        <v>2.3244278587539107</v>
+      </c>
+      <c r="G133" s="6">
+        <v>355.083110954934</v>
+      </c>
+      <c r="H133" s="6">
+        <v>54102.604581580716</v>
+      </c>
+      <c r="I133" s="6">
+        <v>64716.351117303704</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D134" s="8">
         <v>36.02303514448457</v>
       </c>
       <c r="E134" s="9">
+        <v>9798.773717545686</v>
+      </c>
+      <c r="F134" s="9">
+        <v>0</v>
+      </c>
+      <c r="G134" s="9">
+        <v>0</v>
+      </c>
+      <c r="H134" s="9">
+        <v>58080.23093024514</v>
+      </c>
+      <c r="I134" s="9">
         <v>69603.84454573703</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D135" s="5">
-        <v>12206.0338236908</v>
+        <v>12206.033823690794</v>
       </c>
       <c r="E135" s="6">
-        <v>64858.51020181325</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2553.0961850780354</v>
+      </c>
+      <c r="F135" s="6">
+        <v>3335.241649931254</v>
+      </c>
+      <c r="G135" s="6">
+        <v>409.83583442716355</v>
+      </c>
+      <c r="H135" s="6">
+        <v>50893.082674749734</v>
+      </c>
+      <c r="I135" s="6">
+        <v>64869.08396670062</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D136" s="8">
-        <v>2982.85118789301</v>
+        <v>2982.851187893009</v>
       </c>
       <c r="E136" s="9">
-        <v>84946.90553497375</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3676.428763120493</v>
+      </c>
+      <c r="F136" s="9">
+        <v>3565.66408780029</v>
+      </c>
+      <c r="G136" s="9">
+        <v>628.8276176847289</v>
+      </c>
+      <c r="H136" s="9">
+        <v>66789.45348125466</v>
+      </c>
+      <c r="I136" s="9">
+        <v>84963.12928806098</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D137" s="5">
-        <v>299.1853920090474</v>
+        <v>299.18539200904735</v>
       </c>
       <c r="E137" s="6">
-        <v>85152.19758656531</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3675.0705767320455</v>
+      </c>
+      <c r="F137" s="6">
+        <v>3729.2378594460333</v>
+      </c>
+      <c r="G137" s="6">
+        <v>431.0987962689919</v>
+      </c>
+      <c r="H137" s="6">
+        <v>66798.51909476581</v>
+      </c>
+      <c r="I137" s="6">
+        <v>85163.31993588676</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D138" s="8">
-        <v>729.2821715632398</v>
+        <v>729.2821715632394</v>
       </c>
       <c r="E138" s="9">
-        <v>86042.09373283519</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4428.953327299482</v>
+      </c>
+      <c r="F138" s="9">
+        <v>3757.5159372022094</v>
+      </c>
+      <c r="G138" s="9">
+        <v>471.12147000690237</v>
+      </c>
+      <c r="H138" s="9">
+        <v>67552.5984969509</v>
+      </c>
+      <c r="I138" s="9">
+        <v>86054.24866717438</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D139" s="5">
         <v>666.4665153412808</v>
       </c>
       <c r="E139" s="6">
-        <v>83567.87067531761</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2475.2429847818353</v>
+      </c>
+      <c r="F139" s="6">
+        <v>3712.6560776301285</v>
+      </c>
+      <c r="G139" s="6">
+        <v>307.3632320015639</v>
+      </c>
+      <c r="H139" s="6">
+        <v>65525.605545929895</v>
+      </c>
+      <c r="I139" s="6">
+        <v>83575.80064697252</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D140" s="8">
-        <v>965.8732988713545</v>
+        <v>965.8732988713549</v>
       </c>
       <c r="E140" s="9">
-        <v>84520.86710664042</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3399.762348171603</v>
+      </c>
+      <c r="F140" s="9">
+        <v>3507.0376863506335</v>
+      </c>
+      <c r="G140" s="9">
+        <v>343.6459196987694</v>
+      </c>
+      <c r="H140" s="9">
+        <v>66410.99725003235</v>
+      </c>
+      <c r="I140" s="9">
+        <v>84529.73317166978</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D141" s="5">
         <v>317.2384101080767</v>
       </c>
       <c r="E141" s="6">
-        <v>86446.07273473358</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5280.323653002743</v>
+      </c>
+      <c r="F141" s="6">
+        <v>2882.2777004755912</v>
+      </c>
+      <c r="G141" s="6">
+        <v>2730.988768804372</v>
+      </c>
+      <c r="H141" s="6">
+        <v>68802.46077851436</v>
+      </c>
+      <c r="I141" s="6">
+        <v>86516.53224736155</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D142" s="8">
-        <v>7517.335679107698</v>
+        <v>7517.335679107694</v>
       </c>
       <c r="E142" s="9">
-        <v>55879.91152920146</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2001.1442131096892</v>
+      </c>
+      <c r="F142" s="9">
+        <v>3220.9436986456694</v>
+      </c>
+      <c r="G142" s="9">
+        <v>311.7944026054934</v>
+      </c>
+      <c r="H142" s="9">
+        <v>43707.923864041106</v>
+      </c>
+      <c r="I142" s="9">
+        <v>55887.95582506179</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D143" s="5">
-        <v>726.5555994537548</v>
+        <v>726.5555994537546</v>
       </c>
       <c r="E143" s="6">
-        <v>56012.09104650234</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2937.999126360155</v>
+      </c>
+      <c r="F143" s="6">
+        <v>2869.1470055497502</v>
+      </c>
+      <c r="G143" s="6">
+        <v>88.86635221041541</v>
+      </c>
+      <c r="H143" s="6">
+        <v>44154.598204186965</v>
+      </c>
+      <c r="I143" s="6">
+        <v>56014.38379846726</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D144" s="8">
-        <v>1694.4492999933843</v>
+        <v>1694.4492999933857</v>
       </c>
       <c r="E144" s="9">
-        <v>54980.80941369551</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1930.9385481463905</v>
+      </c>
+      <c r="F144" s="9">
+        <v>2370.8672949169923</v>
+      </c>
+      <c r="G144" s="9">
+        <v>298.30088924346666</v>
+      </c>
+      <c r="H144" s="9">
+        <v>43700.70475487058</v>
+      </c>
+      <c r="I144" s="9">
+        <v>54988.50557689935</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D145" s="5">
-        <v>1511.678372843558</v>
+        <v>1511.6783728435587</v>
       </c>
       <c r="E145" s="6">
-        <v>55177.15201627312</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1661.3626010745306</v>
+      </c>
+      <c r="F145" s="6">
+        <v>3101.3829868828448</v>
+      </c>
+      <c r="G145" s="6">
+        <v>272.21990523581536</v>
+      </c>
+      <c r="H145" s="6">
+        <v>43237.27250045313</v>
+      </c>
+      <c r="I145" s="6">
+        <v>55184.17529006671</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D146" s="8">
         <v>2524.8666395831865</v>
       </c>
       <c r="E146" s="9">
-        <v>56492.88467801882</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1660.922388287927</v>
+      </c>
+      <c r="F146" s="9">
+        <v>3883.1591524975947</v>
+      </c>
+      <c r="G146" s="9">
+        <v>114.06373025384916</v>
+      </c>
+      <c r="H146" s="9">
+        <v>43571.48360068226</v>
+      </c>
+      <c r="I146" s="9">
+        <v>56495.827522359315</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D147" s="5">
         <v>1055.3263692924374</v>
       </c>
       <c r="E147" s="6">
-        <v>56760.95785575827</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2749.703244779292</v>
+      </c>
+      <c r="F147" s="6">
+        <v>3422.8437626096734</v>
+      </c>
+      <c r="G147" s="6">
+        <v>1018.0134686658913</v>
+      </c>
+      <c r="H147" s="6">
+        <v>44391.99077976941</v>
+      </c>
+      <c r="I147" s="6">
+        <v>56787.22260414194</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D148" s="8">
-        <v>1705.846956690232</v>
+        <v>1705.8469566902324</v>
       </c>
       <c r="E148" s="9">
-        <v>69298.79497526545</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3021.177060731483</v>
+      </c>
+      <c r="F148" s="9">
+        <v>3436.012838142693</v>
+      </c>
+      <c r="G148" s="9">
+        <v>458.9553948346987</v>
+      </c>
+      <c r="H148" s="9">
+        <v>54760.218655831726</v>
+      </c>
+      <c r="I148" s="9">
+        <v>69310.63602485425</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D149" s="5">
         <v>140.0426196210115</v>
       </c>
       <c r="E149" s="6">
-        <v>69487.44196736632</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2396.024505589301</v>
+      </c>
+      <c r="F149" s="6">
+        <v>4361.466657958425</v>
+      </c>
+      <c r="G149" s="6">
+        <v>178.91316845036857</v>
+      </c>
+      <c r="H149" s="6">
+        <v>54199.50090716135</v>
+      </c>
+      <c r="I149" s="6">
+        <v>69492.05792726912</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D150" s="8">
-        <v>441.34151091332245</v>
+        <v>441.3415109133226</v>
       </c>
       <c r="E150" s="9">
-        <v>68969.1676799323</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2956.6371488884197</v>
+      </c>
+      <c r="F150" s="9">
+        <v>3292.3105130807544</v>
+      </c>
+      <c r="G150" s="9">
+        <v>527.4618682617423</v>
+      </c>
+      <c r="H150" s="9">
+        <v>54609.051602049985</v>
+      </c>
+      <c r="I150" s="9">
+        <v>68982.77619659557</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D151" s="5">
-        <v>354.87260159927064</v>
+        <v>354.8726015992706</v>
       </c>
       <c r="E151" s="6">
-        <v>69377.36091659074</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2771.475051964956</v>
+      </c>
+      <c r="F151" s="6">
+        <v>3658.8458786718766</v>
+      </c>
+      <c r="G151" s="6">
+        <v>162.24390984764435</v>
+      </c>
+      <c r="H151" s="6">
+        <v>54619.36882226016</v>
+      </c>
+      <c r="I151" s="6">
+        <v>69381.54680960697</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D152" s="8">
-        <v>583.3051753203514</v>
+        <v>583.3051753203509</v>
       </c>
       <c r="E152" s="9">
-        <v>69029.80957446653</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2913.408283882668</v>
+      </c>
+      <c r="F152" s="9">
+        <v>3297.152815589207</v>
+      </c>
+      <c r="G152" s="9">
+        <v>108.42612724803973</v>
+      </c>
+      <c r="H152" s="9">
+        <v>54591.95075899378</v>
+      </c>
+      <c r="I152" s="9">
+        <v>69032.6069686445</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D153" s="5">
-        <v>186.28504923627833</v>
+        <v>186.2850492362783</v>
       </c>
       <c r="E153" s="6">
-        <v>70630.51358068314</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4457.184037877515</v>
+      </c>
+      <c r="F153" s="6">
+        <v>3091.0536088408567</v>
+      </c>
+      <c r="G153" s="6">
+        <v>2170.00741049985</v>
+      </c>
+      <c r="H153" s="6">
+        <v>56335.095230470804</v>
+      </c>
+      <c r="I153" s="6">
+        <v>70686.49977377542</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B156" s="10"/>
       <c r="C156" s="10"/>
       <c r="D156" s="10"/>
       <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="10"/>
+      <c r="H156" s="10"/>
+      <c r="I156" s="10"/>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B165" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B166" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B167" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B168" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B169" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B170" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B171" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B172" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B173" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B174" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B175" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B176" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B177" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B178" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B179" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B180" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B181" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B182" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B183" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B184" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B185" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B186" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B187" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B188" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B190" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B192" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B193" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B194" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B195" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B196" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B197" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B198" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>56</v>
+      </c>
+      <c r="B199" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A156:I156"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
